--- a/laporan_padel_dki_jakarta_2026-10-27.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-27.xlsx
@@ -482,16 +482,16 @@
         <v>108</v>
       </c>
       <c r="D2" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp920.000</t>
+          <t>Rp1.000.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -637,16 +637,16 @@
         <v>64</v>
       </c>
       <c r="D7" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp710.000</t>
+          <t>Rp980.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -699,16 +699,16 @@
         <v>68</v>
       </c>
       <c r="D9" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp3.900.000</t>
+          <t>Rp4.125.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -792,16 +792,16 @@
         <v>96</v>
       </c>
       <c r="D12" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>32.3%</t>
+          <t>30.2%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp8.515.000</t>
+          <t>Rp8.125.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -978,16 +978,16 @@
         <v>162</v>
       </c>
       <c r="D18" t="n">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp700.000</t>
+          <t>Rp1.600.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1040,16 +1040,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp600.000</t>
+          <t>Rp1.200.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1133,16 +1133,16 @@
         <v>102</v>
       </c>
       <c r="D23" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp4.100.000</t>
+          <t>Rp4.250.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp2.200.000</t>
+          <t>Rp1.900.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1350,16 +1350,16 @@
         <v>54</v>
       </c>
       <c r="D30" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp1.440.000</t>
+          <t>Rp1.840.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1505,16 +1505,16 @@
         <v>72</v>
       </c>
       <c r="D35" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp2.038.000</t>
+          <t>Rp2.432.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1598,16 +1598,16 @@
         <v>64</v>
       </c>
       <c r="D38" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp5.720.000</t>
+          <t>Rp5.890.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1629,16 +1629,16 @@
         <v>32</v>
       </c>
       <c r="D39" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp600.000</t>
+          <t>Rp1.200.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1722,16 +1722,16 @@
         <v>51</v>
       </c>
       <c r="D42" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp1.725.000</t>
+          <t>Rp1.800.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2187,16 +2187,16 @@
         <v>48</v>
       </c>
       <c r="D57" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp935.000</t>
+          <t>Rp1.050.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2249,16 +2249,16 @@
         <v>32</v>
       </c>
       <c r="D59" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp1.550.000</t>
+          <t>Rp1.775.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2311,16 +2311,16 @@
         <v>80</v>
       </c>
       <c r="D61" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp720.000</t>
+          <t>Rp480.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2342,16 +2342,16 @@
         <v>90</v>
       </c>
       <c r="D62" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp8.480.000</t>
+          <t>Rp8.700.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2683,16 +2683,16 @@
         <v>72</v>
       </c>
       <c r="D73" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp925.000</t>
+          <t>Rp585.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>128</v>
       </c>
       <c r="D78" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp2.350.000</t>
+          <t>Rp2.740.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -3241,16 +3241,16 @@
         <v>119</v>
       </c>
       <c r="D91" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rp6.790.000</t>
+          <t>Rp6.950.000</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -3458,16 +3458,16 @@
         <v>112</v>
       </c>
       <c r="D98" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rp1.845.000</t>
+          <t>Rp1.945.000</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -3611,7 +3611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G72"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3819,16 +3819,16 @@
         <v>162</v>
       </c>
       <c r="D7" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp6.520.000</t>
+          <t>Rp6.250.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -4036,16 +4036,16 @@
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp1.999.000</t>
+          <t>Rp2.199.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4098,16 +4098,16 @@
         <v>105</v>
       </c>
       <c r="D16" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp6.350.000</t>
+          <t>Rp7.250.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -4160,16 +4160,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp4.850.000</t>
+          <t>Rp5.150.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4253,16 +4253,16 @@
         <v>16</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp1.795.000</t>
+          <t>Rp2.094.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -4284,16 +4284,16 @@
         <v>34</v>
       </c>
       <c r="D22" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp2.220.000</t>
+          <t>Rp1.890.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -4649,28 +4649,28 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Padelplay</t>
+          <t>K30 Padel</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>70</v>
+        <v>11</v>
       </c>
       <c r="D34" t="n">
-        <v>63</v>
+        <v>10</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp1.048.000</t>
+          <t>Rp250.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rp130.000 - Rp199.000</t>
+          <t>Rp250.000</t>
         </is>
       </c>
     </row>
@@ -4680,28 +4680,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>La Corte de Padel</t>
+          <t>Padelplay</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>28</v>
+        <v>70</v>
       </c>
       <c r="D35" t="n">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp179.000</t>
+          <t>Rp1.178.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Rp99.000 - Rp179.000</t>
+          <t>Rp130.000 - Rp199.000</t>
         </is>
       </c>
     </row>
@@ -4711,28 +4711,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Racket Kuningan</t>
+          <t>La Corte de Padel</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>159</v>
+        <v>28</v>
       </c>
       <c r="D36" t="n">
-        <v>122</v>
+        <v>27</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp14.500.000</t>
+          <t>Rp179.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Rp150.000 - Rp600.000</t>
+          <t>Rp99.000 - Rp179.000</t>
         </is>
       </c>
     </row>
@@ -4742,28 +4742,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Second Serve Padel</t>
+          <t>Racket Kuningan</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>45</v>
+        <v>159</v>
       </c>
       <c r="D37" t="n">
-        <v>39</v>
+        <v>122</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp2.050.000</t>
+          <t>Rp14.500.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Rp275.000 - Rp375.000</t>
+          <t>Rp150.000 - Rp600.000</t>
         </is>
       </c>
     </row>
@@ -4773,28 +4773,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>The Rooftop Kyzn Kuningan</t>
+          <t>Second Serve Padel</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="D38" t="n">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp6.200.000</t>
+          <t>Rp2.050.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rp300.000 - Rp1.000.000</t>
+          <t>Rp275.000 - Rp375.000</t>
         </is>
       </c>
     </row>
@@ -4804,28 +4804,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Space Padel ITC Fatmawati</t>
+          <t>The Rooftop Kyzn Kuningan</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="D39" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp800.000</t>
+          <t>Rp6.800.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rp125.000 - Rp200.000</t>
+          <t>Rp300.000 - Rp1.000.000</t>
         </is>
       </c>
     </row>
@@ -4835,28 +4835,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Victoria Social Club - Kemang</t>
+          <t>Space Padel ITC Fatmawati</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D40" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp3.900.000</t>
+          <t>Rp800.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Rp300.000 - Rp499.000</t>
+          <t>Rp125.000 - Rp200.000</t>
         </is>
       </c>
     </row>
@@ -4866,28 +4866,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Metropolar Padel Bripens Gatsu</t>
+          <t>Victoria Social Club - Kemang</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D41" t="n">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>60.4%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp9.200.000</t>
+          <t>Rp3.900.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Rp250.000 - Rp400.000</t>
+          <t>Rp300.000 - Rp499.000</t>
         </is>
       </c>
     </row>
@@ -4897,28 +4897,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>TOM'S PADEL by Sira</t>
+          <t>Metropolar Padel Bripens Gatsu</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="D42" t="n">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp1.600.000</t>
+          <t>Rp8.950.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Rp200.000</t>
+          <t>Rp250.000 - Rp400.000</t>
         </is>
       </c>
     </row>
@@ -4928,28 +4928,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>MMS ARENA</t>
+          <t>TOM'S PADEL by Sira</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="D43" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp7.300.000</t>
+          <t>Rp1.600.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Rp180.000 - Rp1.100.000</t>
+          <t>Rp200.000</t>
         </is>
       </c>
     </row>
@@ -4959,28 +4959,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BM Padel Jagakarsa</t>
+          <t>MMS ARENA</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="D44" t="n">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp1.480.000</t>
+          <t>Rp7.300.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Rp185.000</t>
+          <t>Rp180.000 - Rp1.100.000</t>
         </is>
       </c>
     </row>
@@ -4990,28 +4990,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Serve and Rally Reserve</t>
+          <t>BM Padel Jagakarsa</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>11</v>
+        <v>54</v>
       </c>
       <c r="D45" t="n">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp1.480.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rp250.000 - Rp425.000</t>
+          <t>Rp185.000</t>
         </is>
       </c>
     </row>
@@ -5021,28 +5021,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Fourthwall</t>
+          <t>Serve and Rally Reserve</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D46" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp4.800.000</t>
+          <t>Rp0</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp250.000 - Rp425.000</t>
         </is>
       </c>
     </row>
@@ -5052,28 +5052,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Binakarsa Green Courts</t>
+          <t>Fourthwall</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="D47" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp2.988.000</t>
+          <t>Rp4.800.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Rp200.000 - Rp332.000</t>
+          <t>Rp1.200.000</t>
         </is>
       </c>
     </row>
@@ -5083,28 +5083,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Desimal Padel</t>
+          <t>Binakarsa Green Courts</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>80</v>
+        <v>32</v>
       </c>
       <c r="D48" t="n">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp3.250.000</t>
+          <t>Rp2.988.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Rp125.000 - Rp225.000</t>
+          <t>Rp200.000 - Rp332.000</t>
         </is>
       </c>
     </row>
@@ -5114,23 +5114,23 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>AIR Padel Active</t>
+          <t>Desimal Padel</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D49" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp3.750.000</t>
+          <t>Rp3.250.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5145,28 +5145,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>GOAT Arena Cibis</t>
+          <t>AIR Padel Active</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="D50" t="n">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp8.352.000</t>
+          <t>Rp3.750.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Rp300.000 - Rp396.000</t>
+          <t>Rp125.000 - Rp225.000</t>
         </is>
       </c>
     </row>
@@ -5176,28 +5176,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Padel Parc MT Haryono By DOOgether</t>
+          <t>GOAT Arena Cibis</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="D51" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp5.750.000</t>
+          <t>Rp8.352.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Rp150.000 - Rp400.000</t>
+          <t>Rp300.000 - Rp396.000</t>
         </is>
       </c>
     </row>
@@ -5207,28 +5207,28 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Clubhouse Gandaria</t>
+          <t>Padel Parc MT Haryono By DOOgether</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D52" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp6.450.000</t>
+          <t>Rp5.450.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Rp250.000 - Rp350.000</t>
+          <t>Rp150.000 - Rp400.000</t>
         </is>
       </c>
     </row>
@@ -5238,28 +5238,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>All Play Kemang | Padel &amp; Pickle</t>
+          <t>Clubhouse Gandaria</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="D53" t="n">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp2.160.000</t>
+          <t>Rp6.450.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Rp200.000 - Rp360.000</t>
+          <t>Rp250.000 - Rp350.000</t>
         </is>
       </c>
     </row>
@@ -5269,28 +5269,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Trilogi Arena By Duale</t>
+          <t>All Play Kemang | Padel &amp; Pickle</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D54" t="n">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp7.335.000</t>
+          <t>Rp2.160.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Rp275.000 - Rp330.000</t>
+          <t>Rp200.000 - Rp360.000</t>
         </is>
       </c>
     </row>
@@ -5300,28 +5300,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Lifestyle Capital Club (LCC): Padel Court, Padel/Tennis/Golf Simulator, Cafe &amp; Working Space</t>
+          <t>Trilogi Arena By Duale</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="D55" t="n">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp2.200.000</t>
+          <t>Rp7.335.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Rp150.000 - Rp350.000</t>
+          <t>Rp275.000 - Rp330.000</t>
         </is>
       </c>
     </row>
@@ -5331,28 +5331,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Padel un Terra Simulator</t>
+          <t>Lifestyle Capital Club (LCC): Padel Court, Padel/Tennis/Golf Simulator, Cafe &amp; Working Space</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D56" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rp71.000</t>
+          <t>Rp2.200.000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Rp53.000 - Rp71.000</t>
+          <t>Rp150.000 - Rp350.000</t>
         </is>
       </c>
     </row>
@@ -5362,28 +5362,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Padel Venue</t>
+          <t>Padel un Terra Simulator</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="D57" t="n">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp350.000</t>
+          <t>Rp71.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Rp150.000 - Rp175.000</t>
+          <t>Rp53.000 - Rp71.000</t>
         </is>
       </c>
     </row>
@@ -5393,28 +5393,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>4-Play Padel Simulator</t>
+          <t>Padel Venue</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>124</v>
+        <v>51</v>
       </c>
       <c r="D58" t="n">
-        <v>117</v>
+        <v>49</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp780.000</t>
+          <t>Rp350.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Rp100.000 - Rp120.000</t>
+          <t>Rp150.000 - Rp175.000</t>
         </is>
       </c>
     </row>
@@ -5424,28 +5424,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Round Padel</t>
+          <t>4-Play Padel Simulator</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>32</v>
+        <v>124</v>
       </c>
       <c r="D59" t="n">
-        <v>26</v>
+        <v>117</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp1.410.000</t>
+          <t>Rp780.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Rp199.000 - Rp275.000</t>
+          <t>Rp100.000 - Rp120.000</t>
         </is>
       </c>
     </row>
@@ -5455,28 +5455,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Oasis Padel Kuningan</t>
+          <t>Round Padel</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="D60" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp7.575.000</t>
+          <t>Rp1.410.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Rp250.000 - Rp475.000</t>
+          <t>Rp199.000 - Rp275.000</t>
         </is>
       </c>
     </row>
@@ -5486,28 +5486,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Dome Padel, Tebet</t>
+          <t>Oasis Padel Kuningan</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="D61" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp2.135.000</t>
+          <t>Rp7.575.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Rp175.000 - Rp280.000</t>
+          <t>Rp250.000 - Rp475.000</t>
         </is>
       </c>
     </row>
@@ -5517,28 +5517,28 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Jungle Padel Jakarta</t>
+          <t>Dome Padel, Tebet</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="D62" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp8.950.000</t>
+          <t>Rp2.135.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Rp450.000 - Rp600.000</t>
+          <t>Rp175.000 - Rp280.000</t>
         </is>
       </c>
     </row>
@@ -5548,28 +5548,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Padel House 54</t>
+          <t>Jungle Padel Jakarta</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="D63" t="n">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp2.079.000</t>
+          <t>Rp8.950.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Rp189.000 - Rp299.000</t>
+          <t>Rp450.000 - Rp600.000</t>
         </is>
       </c>
     </row>
@@ -5579,28 +5579,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Grand Sports Padel</t>
+          <t>Padel House 54</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>90</v>
+        <v>34</v>
       </c>
       <c r="D64" t="n">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rp9.700.000</t>
+          <t>Rp2.079.000</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Rp250.000 - Rp400.000</t>
+          <t>Rp189.000 - Rp299.000</t>
         </is>
       </c>
     </row>
@@ -5610,28 +5610,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Padel Parc Arkadia</t>
+          <t>Grand Sports Padel</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="D65" t="n">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rp6.714.000</t>
+          <t>Rp10.200.000</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Rp180.000 - Rp297.000</t>
+          <t>Rp250.000 - Rp400.000</t>
         </is>
       </c>
     </row>
@@ -5641,28 +5641,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Playfieldcourt Signature</t>
+          <t>Padel Parc Arkadia</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>234</v>
+        <v>102</v>
       </c>
       <c r="D66" t="n">
-        <v>201</v>
+        <v>79</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rp4.084.000</t>
+          <t>Rp6.714.000</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Rp88.000 - Rp200.000</t>
+          <t>Rp180.000 - Rp297.000</t>
         </is>
       </c>
     </row>
@@ -5672,28 +5672,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Fork Padel</t>
+          <t>Playfieldcourt Signature</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>72</v>
+        <v>234</v>
       </c>
       <c r="D67" t="n">
-        <v>60</v>
+        <v>201</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp4.200.000</t>
+          <t>Rp4.084.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Rp180.000 - Rp350.000</t>
+          <t>Rp88.000 - Rp200.000</t>
         </is>
       </c>
     </row>
@@ -5703,28 +5703,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>T3 Sports &amp; Lifestyle</t>
+          <t>Fork Padel</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>144</v>
+        <v>72</v>
       </c>
       <c r="D68" t="n">
-        <v>127</v>
+        <v>60</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp8.450.000</t>
+          <t>Rp4.200.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Rp150.000 - Rp600.000</t>
+          <t>Rp180.000 - Rp350.000</t>
         </is>
       </c>
     </row>
@@ -5734,28 +5734,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Mpadl</t>
+          <t>T3 Sports &amp; Lifestyle</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>30</v>
+        <v>144</v>
       </c>
       <c r="D69" t="n">
-        <v>10</v>
+        <v>127</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp2.675.000</t>
+          <t>Rp8.450.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Rp125.000 - Rp150.000</t>
+          <t>Rp150.000 - Rp600.000</t>
         </is>
       </c>
     </row>
@@ -5765,28 +5765,28 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>PPPLATZ</t>
+          <t>Mpadl</t>
         </is>
       </c>
       <c r="C70" t="n">
         <v>30</v>
       </c>
       <c r="D70" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp1.865.000</t>
+          <t>Rp2.675.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Rp325.000 - Rp385.000</t>
+          <t>Rp125.000 - Rp150.000</t>
         </is>
       </c>
     </row>
@@ -5796,28 +5796,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Republic Premier</t>
+          <t>PPPLATZ</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>162</v>
+        <v>30</v>
       </c>
       <c r="D71" t="n">
-        <v>129</v>
+        <v>25</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rp17.450.000</t>
+          <t>Rp1.865.000</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Rp350.000 - Rp550.000</t>
+          <t>Rp325.000 - Rp385.000</t>
         </is>
       </c>
     </row>
@@ -5827,26 +5827,57 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
+          <t>Republic Premier</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>162</v>
+      </c>
+      <c r="D72" t="n">
+        <v>129</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>20.4%</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Rp17.450.000</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Rp350.000 - Rp550.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
           <t>Margot Padel</t>
         </is>
       </c>
-      <c r="C72" t="n">
+      <c r="C73" t="n">
         <v>90</v>
       </c>
-      <c r="D72" t="n">
+      <c r="D73" t="n">
         <v>71</v>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>21.1%</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>Rp6.050.000</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>Rp250.000 - Rp450.000</t>
         </is>
@@ -6009,16 +6040,16 @@
         <v>102</v>
       </c>
       <c r="D5" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp4.950.000</t>
+          <t>Rp5.700.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6111,7 +6142,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp31.800.000</t>
+          <t>Rp31.650.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6319,16 +6350,16 @@
         <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp3.800.000</t>
+          <t>Rp3.500.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6505,16 +6536,16 @@
         <v>64</v>
       </c>
       <c r="D21" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp4.992.000</t>
+          <t>Rp5.391.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -6618,16 +6649,16 @@
         <v>86</v>
       </c>
       <c r="D3" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>5.8%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp5.100.000</t>
+          <t>Rp5.250.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6711,16 +6742,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp11.720.000</t>
+          <t>Rp11.900.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6866,16 +6897,16 @@
         <v>216</v>
       </c>
       <c r="D11" t="n">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp15.842.500</t>
+          <t>Rp16.402.500</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -7052,16 +7083,16 @@
         <v>144</v>
       </c>
       <c r="D17" t="n">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp4.500.000</t>
+          <t>Rp4.900.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7331,16 +7362,16 @@
         <v>108</v>
       </c>
       <c r="D26" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp5.790.000</t>
+          <t>Rp6.130.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -7424,16 +7455,16 @@
         <v>64</v>
       </c>
       <c r="D29" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp3.075.000</t>
+          <t>Rp3.375.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -7610,16 +7641,16 @@
         <v>187</v>
       </c>
       <c r="D35" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>36.9%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp13.200.000</t>
+          <t>Rp13.125.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7858,16 +7889,16 @@
         <v>80</v>
       </c>
       <c r="D43" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp2.900.000</t>
+          <t>Rp2.300.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -8075,16 +8106,16 @@
         <v>102</v>
       </c>
       <c r="D50" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp13.654.000</t>
+          <t>Rp13.883.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -8106,16 +8137,16 @@
         <v>98</v>
       </c>
       <c r="D51" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp2.980.000</t>
+          <t>Rp2.530.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -8281,16 +8312,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>22.8%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp5.410.000</t>
+          <t>Rp5.740.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8529,16 +8560,16 @@
         <v>72</v>
       </c>
       <c r="D11" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp5.620.000</t>
+          <t>Rp6.070.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -8591,16 +8622,16 @@
         <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp3.599.992</t>
+          <t>Rp3.849.992</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -8684,16 +8715,16 @@
         <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp3.315.000</t>
+          <t>Rp4.315.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -8777,16 +8808,16 @@
         <v>102</v>
       </c>
       <c r="D19" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>36.3%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp13.870.000</t>
+          <t>Rp14.350.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -9025,16 +9056,16 @@
         <v>32</v>
       </c>
       <c r="D27" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp250.000</t>
+          <t>Rp375.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -9304,16 +9335,16 @@
         <v>72</v>
       </c>
       <c r="D36" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp1.337.000</t>
+          <t>Rp1.436.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -9335,16 +9366,16 @@
         <v>54</v>
       </c>
       <c r="D37" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp3.340.000</t>
+          <t>Rp3.525.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -9459,16 +9490,16 @@
         <v>64</v>
       </c>
       <c r="D41" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp1.000.000</t>
+          <t>Rp1.400.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-27.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-27.xlsx
@@ -482,16 +482,16 @@
         <v>108</v>
       </c>
       <c r="D2" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.000.000</t>
+          <t>Rp1.160.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -668,16 +668,16 @@
         <v>64</v>
       </c>
       <c r="D8" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp3.280.000</t>
+          <t>Rp2.960.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -792,16 +792,16 @@
         <v>96</v>
       </c>
       <c r="D12" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp8.125.000</t>
+          <t>Rp8.455.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -978,16 +978,16 @@
         <v>162</v>
       </c>
       <c r="D18" t="n">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp1.600.000</t>
+          <t>Rp2.000.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1040,16 +1040,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp1.350.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp2.475.000</t>
+          <t>Rp2.850.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp1.900.000</t>
+          <t>Rp1.775.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1381,16 +1381,16 @@
         <v>102</v>
       </c>
       <c r="D31" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp1.627.000</t>
+          <t>Rp1.847.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1443,16 +1443,16 @@
         <v>85</v>
       </c>
       <c r="D33" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp4.570.000</t>
+          <t>Rp3.400.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1474,16 +1474,16 @@
         <v>68</v>
       </c>
       <c r="D34" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp1.755.000</t>
+          <t>Rp2.675.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1598,16 +1598,16 @@
         <v>64</v>
       </c>
       <c r="D38" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp5.890.000</t>
+          <t>Rp6.230.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1691,16 +1691,16 @@
         <v>54</v>
       </c>
       <c r="D41" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp1.080.000</t>
+          <t>Rp1.470.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1753,16 +1753,16 @@
         <v>234</v>
       </c>
       <c r="D43" t="n">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp7.864.000</t>
+          <t>Rp8.564.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -1815,16 +1815,16 @@
         <v>198</v>
       </c>
       <c r="D45" t="n">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp1.650.000</t>
+          <t>Rp1.950.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -1877,16 +1877,16 @@
         <v>42</v>
       </c>
       <c r="D47" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp100.000</t>
+          <t>Rp1.000.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -1939,16 +1939,16 @@
         <v>105</v>
       </c>
       <c r="D49" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp5.150.000</t>
+          <t>Rp3.550.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2187,16 +2187,16 @@
         <v>48</v>
       </c>
       <c r="D57" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp1.050.000</t>
+          <t>Rp1.410.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2311,16 +2311,16 @@
         <v>80</v>
       </c>
       <c r="D61" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp480.000</t>
+          <t>Rp360.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2342,16 +2342,16 @@
         <v>90</v>
       </c>
       <c r="D62" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp8.700.000</t>
+          <t>Rp8.800.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2373,16 +2373,16 @@
         <v>68</v>
       </c>
       <c r="D63" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp2.045.000</t>
+          <t>Rp2.135.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2435,16 +2435,16 @@
         <v>34</v>
       </c>
       <c r="D65" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rp300.000</t>
+          <t>Rp900.000</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -2559,16 +2559,16 @@
         <v>34</v>
       </c>
       <c r="D69" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp940.000</t>
+          <t>Rp1.435.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2931,16 +2931,16 @@
         <v>126</v>
       </c>
       <c r="D81" t="n">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rp3.473.000</t>
+          <t>Rp4.269.000</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -2962,16 +2962,16 @@
         <v>54</v>
       </c>
       <c r="D82" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rp1.093.000</t>
+          <t>Rp1.390.000</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -3055,16 +3055,16 @@
         <v>135</v>
       </c>
       <c r="D85" t="n">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rp6.900.000</t>
+          <t>Rp8.655.000</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3086,16 +3086,16 @@
         <v>96</v>
       </c>
       <c r="D86" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rp6.400.000</t>
+          <t>Rp7.300.000</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3312,7 +3312,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rp448.000</t>
+          <t>Rp396.000</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -3726,16 +3726,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp5.400.000</t>
+          <t>Rp6.000.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3819,16 +3819,16 @@
         <v>162</v>
       </c>
       <c r="D7" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp6.250.000</t>
+          <t>Rp6.400.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3974,16 +3974,16 @@
         <v>51</v>
       </c>
       <c r="D12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>60.8%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp7.735.000</t>
+          <t>Rp7.925.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -4005,16 +4005,16 @@
         <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp3.770.000</t>
+          <t>Rp3.955.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -4036,16 +4036,16 @@
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp2.199.000</t>
+          <t>Rp2.499.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4439,16 +4439,16 @@
         <v>45</v>
       </c>
       <c r="D27" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp1.794.000</t>
+          <t>Rp2.392.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4687,16 +4687,16 @@
         <v>70</v>
       </c>
       <c r="D35" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp1.178.000</t>
+          <t>Rp1.438.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -4749,16 +4749,16 @@
         <v>159</v>
       </c>
       <c r="D37" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp14.500.000</t>
+          <t>Rp14.650.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4935,16 +4935,16 @@
         <v>64</v>
       </c>
       <c r="D43" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp1.600.000</t>
+          <t>Rp2.000.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -5121,16 +5121,16 @@
         <v>80</v>
       </c>
       <c r="D49" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp3.250.000</t>
+          <t>Rp3.375.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5152,16 +5152,16 @@
         <v>84</v>
       </c>
       <c r="D50" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp3.750.000</t>
+          <t>Rp4.200.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5245,16 +5245,16 @@
         <v>60</v>
       </c>
       <c r="D53" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp6.450.000</t>
+          <t>Rp7.550.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -5369,16 +5369,16 @@
         <v>75</v>
       </c>
       <c r="D57" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp71.000</t>
+          <t>Rp142.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5524,16 +5524,16 @@
         <v>36</v>
       </c>
       <c r="D62" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp2.135.000</t>
+          <t>Rp2.415.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -5586,16 +5586,16 @@
         <v>34</v>
       </c>
       <c r="D64" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rp2.079.000</t>
+          <t>Rp1.701.000</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -5679,16 +5679,16 @@
         <v>234</v>
       </c>
       <c r="D67" t="n">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp4.084.000</t>
+          <t>Rp4.264.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -6009,16 +6009,16 @@
         <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp950.000</t>
+          <t>Rp1.075.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6040,16 +6040,16 @@
         <v>102</v>
       </c>
       <c r="D5" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp5.700.000</t>
+          <t>Rp6.200.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6071,16 +6071,16 @@
         <v>36</v>
       </c>
       <c r="D6" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp1.490.000</t>
+          <t>Rp2.010.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6164,16 +6164,16 @@
         <v>54</v>
       </c>
       <c r="D9" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp1.000.000</t>
+          <t>Rp1.350.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6350,16 +6350,16 @@
         <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp3.500.000</t>
+          <t>Rp3.650.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6474,16 +6474,16 @@
         <v>48</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp1.350.000</t>
+          <t>Rp1.550.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -6505,16 +6505,16 @@
         <v>15</v>
       </c>
       <c r="D20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp684.000</t>
+          <t>Rp852.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -6536,16 +6536,16 @@
         <v>64</v>
       </c>
       <c r="D21" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp5.391.000</t>
+          <t>Rp5.790.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -6773,16 +6773,16 @@
         <v>144</v>
       </c>
       <c r="D7" t="n">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>28.5%</t>
+          <t>32.6%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp12.375.000</t>
+          <t>Rp14.475.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6835,16 +6835,16 @@
         <v>85</v>
       </c>
       <c r="D9" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>50.6%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp9.019.000</t>
+          <t>Rp9.455.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6897,16 +6897,16 @@
         <v>216</v>
       </c>
       <c r="D11" t="n">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp16.402.500</t>
+          <t>Rp17.161.500</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6990,16 +6990,16 @@
         <v>72</v>
       </c>
       <c r="D14" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp4.270.000</t>
+          <t>Rp3.720.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -7021,16 +7021,16 @@
         <v>96</v>
       </c>
       <c r="D15" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp1.500.000</t>
+          <t>Rp900.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -7052,16 +7052,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp5.450.000</t>
+          <t>Rp5.650.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7083,16 +7083,16 @@
         <v>144</v>
       </c>
       <c r="D17" t="n">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp4.900.000</t>
+          <t>Rp5.050.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7207,16 +7207,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>42.5%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp21.700.000</t>
+          <t>Rp22.000.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp3.847.000</t>
+          <t>Rp4.197.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7424,16 +7424,16 @@
         <v>96</v>
       </c>
       <c r="D28" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp3.550.000</t>
+          <t>Rp4.050.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -7517,16 +7517,16 @@
         <v>96</v>
       </c>
       <c r="D31" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp3.863.000</t>
+          <t>Rp4.363.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -7548,16 +7548,16 @@
         <v>96</v>
       </c>
       <c r="D32" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp2.225.000</t>
+          <t>Rp2.575.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -7610,16 +7610,16 @@
         <v>108</v>
       </c>
       <c r="D34" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp8.945.000</t>
+          <t>Rp8.750.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7641,16 +7641,16 @@
         <v>187</v>
       </c>
       <c r="D35" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>36.9%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp13.125.000</t>
+          <t>Rp13.175.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7672,16 +7672,16 @@
         <v>67</v>
       </c>
       <c r="D36" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp3.356.000</t>
+          <t>Rp3.932.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -7734,16 +7734,16 @@
         <v>170</v>
       </c>
       <c r="D38" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp4.750.000</t>
+          <t>Rp4.900.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -7827,16 +7827,16 @@
         <v>150</v>
       </c>
       <c r="D41" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>48.7%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp21.950.000</t>
+          <t>Rp22.375.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -8199,16 +8199,16 @@
         <v>90</v>
       </c>
       <c r="D53" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp6.200.000</t>
+          <t>Rp6.600.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -8374,16 +8374,16 @@
         <v>86</v>
       </c>
       <c r="D5" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp5.100.000</t>
+          <t>Rp5.800.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -8529,16 +8529,16 @@
         <v>108</v>
       </c>
       <c r="D10" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp1.140.000</t>
+          <t>Rp1.470.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8622,16 +8622,16 @@
         <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp3.849.992</t>
+          <t>Rp4.174.991</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -8715,16 +8715,16 @@
         <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp4.315.000</t>
+          <t>Rp3.910.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -8963,16 +8963,16 @@
         <v>54</v>
       </c>
       <c r="D24" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp4.124.995</t>
+          <t>Rp4.574.994</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -9087,16 +9087,16 @@
         <v>36</v>
       </c>
       <c r="D28" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp1.100.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -9149,16 +9149,16 @@
         <v>54</v>
       </c>
       <c r="D30" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp2.750.000</t>
+          <t>Rp2.900.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -9211,16 +9211,16 @@
         <v>34</v>
       </c>
       <c r="D32" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp1.765.000</t>
+          <t>Rp2.285.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -9304,16 +9304,16 @@
         <v>51</v>
       </c>
       <c r="D35" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp1.030.000</t>
+          <t>Rp1.770.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -9459,16 +9459,16 @@
         <v>68</v>
       </c>
       <c r="D40" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp796.000</t>
+          <t>Rp1.592.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-27.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-27.xlsx
@@ -482,16 +482,16 @@
         <v>108</v>
       </c>
       <c r="D2" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.160.000</t>
+          <t>Rp1.400.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -544,16 +544,16 @@
         <v>144</v>
       </c>
       <c r="D4" t="n">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp11.500.000</t>
+          <t>Rp12.700.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -575,16 +575,16 @@
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp396.000</t>
+          <t>Rp696.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -637,16 +637,16 @@
         <v>64</v>
       </c>
       <c r="D7" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp980.000</t>
+          <t>Rp1.385.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -668,16 +668,16 @@
         <v>64</v>
       </c>
       <c r="D8" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp2.960.000</t>
+          <t>Rp4.880.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -699,16 +699,16 @@
         <v>68</v>
       </c>
       <c r="D9" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp4.125.000</t>
+          <t>Rp4.575.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp5.773.986</t>
+          <t>Rp5.572.987</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -792,16 +792,16 @@
         <v>96</v>
       </c>
       <c r="D12" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp8.455.000</t>
+          <t>Rp9.455.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -823,16 +823,16 @@
         <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp5.500.000</t>
+          <t>Rp6.000.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>162</v>
       </c>
       <c r="D14" t="n">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>37.7%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp12.240.000</t>
+          <t>Rp13.714.500</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -885,16 +885,16 @@
         <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp3.725.000</t>
+          <t>Rp4.425.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -916,16 +916,16 @@
         <v>112</v>
       </c>
       <c r="D16" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp3.520.000</t>
+          <t>Rp2.784.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -947,16 +947,16 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp300.000</t>
+          <t>Rp600.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -978,16 +978,16 @@
         <v>162</v>
       </c>
       <c r="D18" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp2.000.000</t>
+          <t>Rp1.700.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1040,16 +1040,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp1.350.000</t>
+          <t>Rp1.788.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1102,16 +1102,16 @@
         <v>136</v>
       </c>
       <c r="D22" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>30.1%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp13.242.000</t>
+          <t>Rp14.538.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1164,16 +1164,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp4.050.000</t>
+          <t>Rp5.450.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1192,19 +1192,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="D25" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp2.850.000</t>
+          <t>Rp3.600.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp1.775.000</t>
+          <t>Rp1.450.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1257,16 +1257,16 @@
         <v>15</v>
       </c>
       <c r="D27" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp375.000</t>
+          <t>Rp975.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1381,16 +1381,16 @@
         <v>102</v>
       </c>
       <c r="D31" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp1.847.000</t>
+          <t>Rp2.243.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1443,16 +1443,16 @@
         <v>85</v>
       </c>
       <c r="D33" t="n">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp3.400.000</t>
+          <t>Rp1.615.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1474,16 +1474,16 @@
         <v>68</v>
       </c>
       <c r="D34" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp2.675.000</t>
+          <t>Rp3.595.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1505,16 +1505,16 @@
         <v>72</v>
       </c>
       <c r="D35" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp2.432.000</t>
+          <t>Rp2.550.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1567,16 +1567,16 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp3.590.000</t>
+          <t>Rp3.840.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1598,16 +1598,16 @@
         <v>64</v>
       </c>
       <c r="D38" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp6.230.000</t>
+          <t>Rp6.400.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1691,16 +1691,16 @@
         <v>54</v>
       </c>
       <c r="D41" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp1.470.000</t>
+          <t>Rp1.665.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1784,16 +1784,16 @@
         <v>72</v>
       </c>
       <c r="D44" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp8.225.000</t>
+          <t>Rp8.324.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -1846,16 +1846,16 @@
         <v>60</v>
       </c>
       <c r="D46" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp2.100.000</t>
+          <t>Rp2.520.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -1939,16 +1939,16 @@
         <v>105</v>
       </c>
       <c r="D49" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp3.550.000</t>
+          <t>Rp4.150.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2001,16 +2001,16 @@
         <v>56</v>
       </c>
       <c r="D51" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp3.300.000</t>
+          <t>Rp4.950.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2032,16 +2032,16 @@
         <v>64</v>
       </c>
       <c r="D52" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp4.320.000</t>
+          <t>Rp6.624.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2249,16 +2249,16 @@
         <v>32</v>
       </c>
       <c r="D59" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp1.775.000</t>
+          <t>Rp2.550.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2370,24 +2370,24 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D63" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp2.135.000</t>
+          <t>Rp3.045.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Rp75.000 - Rp380.000</t>
+          <t>Rp75.000 - Rp180.000</t>
         </is>
       </c>
     </row>
@@ -2590,16 +2590,16 @@
         <v>176</v>
       </c>
       <c r="D70" t="n">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp1.245.000</t>
+          <t>Rp2.241.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2652,16 +2652,16 @@
         <v>68</v>
       </c>
       <c r="D72" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp180.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -2683,16 +2683,16 @@
         <v>72</v>
       </c>
       <c r="D73" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp585.000</t>
+          <t>Rp925.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>128</v>
       </c>
       <c r="D78" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp2.740.000</t>
+          <t>Rp2.985.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -2869,16 +2869,16 @@
         <v>108</v>
       </c>
       <c r="D79" t="n">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rp2.325.000</t>
+          <t>Rp2.850.000</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -2931,16 +2931,16 @@
         <v>126</v>
       </c>
       <c r="D81" t="n">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rp4.269.000</t>
+          <t>Rp5.163.000</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3055,16 +3055,16 @@
         <v>135</v>
       </c>
       <c r="D85" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rp8.655.000</t>
+          <t>Rp8.880.000</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3086,16 +3086,16 @@
         <v>96</v>
       </c>
       <c r="D86" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rp7.300.000</t>
+          <t>Rp7.900.000</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3179,16 +3179,16 @@
         <v>138</v>
       </c>
       <c r="D89" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rp5.500.000</t>
+          <t>Rp5.950.000</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3303,16 +3303,16 @@
         <v>28</v>
       </c>
       <c r="D93" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rp396.000</t>
+          <t>Rp495.000</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -3334,16 +3334,16 @@
         <v>85</v>
       </c>
       <c r="D94" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rp943.000</t>
+          <t>Rp1.008.000</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -3396,16 +3396,16 @@
         <v>80</v>
       </c>
       <c r="D96" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rp4.027.000</t>
+          <t>Rp4.525.000</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3664,16 +3664,16 @@
         <v>36</v>
       </c>
       <c r="D2" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp891.000</t>
+          <t>Rp1.053.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -3726,16 +3726,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp6.000.000</t>
+          <t>Rp6.600.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3850,16 +3850,16 @@
         <v>32</v>
       </c>
       <c r="D8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp4.700.000</t>
+          <t>Rp5.250.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -4036,16 +4036,16 @@
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>37.1%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp2.499.000</t>
+          <t>Rp2.599.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4098,16 +4098,16 @@
         <v>105</v>
       </c>
       <c r="D16" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp7.250.000</t>
+          <t>Rp8.950.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -4129,16 +4129,16 @@
         <v>65</v>
       </c>
       <c r="D17" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp5.220.000</t>
+          <t>Rp3.600.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -4160,16 +4160,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp5.150.000</t>
+          <t>Rp6.350.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4222,16 +4222,16 @@
         <v>18</v>
       </c>
       <c r="D20" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp150.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -4253,16 +4253,16 @@
         <v>16</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp2.094.000</t>
+          <t>Rp2.792.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -4284,16 +4284,16 @@
         <v>34</v>
       </c>
       <c r="D22" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp1.890.000</t>
+          <t>Rp2.085.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -4315,16 +4315,16 @@
         <v>36</v>
       </c>
       <c r="D23" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp2.800.000</t>
+          <t>Rp3.150.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -4346,16 +4346,16 @@
         <v>53</v>
       </c>
       <c r="D24" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp10.850.000</t>
+          <t>Rp10.450.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -4470,16 +4470,16 @@
         <v>170</v>
       </c>
       <c r="D28" t="n">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp14.700.000</t>
+          <t>Rp16.200.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4625,16 +4625,16 @@
         <v>90</v>
       </c>
       <c r="D33" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp3.375.000</t>
+          <t>Rp3.825.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4656,16 +4656,16 @@
         <v>11</v>
       </c>
       <c r="D34" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp250.000</t>
+          <t>Rp750.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4687,16 +4687,16 @@
         <v>70</v>
       </c>
       <c r="D35" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp1.438.000</t>
+          <t>Rp1.836.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -4749,16 +4749,16 @@
         <v>159</v>
       </c>
       <c r="D37" t="n">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>27.0%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp14.650.000</t>
+          <t>Rp16.900.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4780,16 +4780,16 @@
         <v>45</v>
       </c>
       <c r="D38" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp2.050.000</t>
+          <t>Rp4.300.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -4904,16 +4904,16 @@
         <v>48</v>
       </c>
       <c r="D42" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp8.950.000</t>
+          <t>Rp8.550.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -4997,16 +4997,16 @@
         <v>54</v>
       </c>
       <c r="D45" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp1.480.000</t>
+          <t>Rp2.220.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -5028,16 +5028,16 @@
         <v>11</v>
       </c>
       <c r="D46" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp650.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -5059,16 +5059,16 @@
         <v>6</v>
       </c>
       <c r="D47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp4.800.000</t>
+          <t>Rp6.000.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -5152,16 +5152,16 @@
         <v>84</v>
       </c>
       <c r="D50" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>27.4%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp4.200.000</t>
+          <t>Rp4.425.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5307,16 +5307,16 @@
         <v>68</v>
       </c>
       <c r="D55" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp7.335.000</t>
+          <t>Rp8.875.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -5369,16 +5369,16 @@
         <v>75</v>
       </c>
       <c r="D57" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp142.000</t>
+          <t>Rp266.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5400,16 +5400,16 @@
         <v>51</v>
       </c>
       <c r="D58" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp350.000</t>
+          <t>Rp0</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -5493,16 +5493,16 @@
         <v>45</v>
       </c>
       <c r="D61" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp7.575.000</t>
+          <t>Rp8.525.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -5617,16 +5617,16 @@
         <v>90</v>
       </c>
       <c r="D65" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rp10.200.000</t>
+          <t>Rp9.400.000</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -5679,16 +5679,16 @@
         <v>234</v>
       </c>
       <c r="D67" t="n">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp4.264.000</t>
+          <t>Rp4.414.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5741,16 +5741,16 @@
         <v>144</v>
       </c>
       <c r="D69" t="n">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp8.450.000</t>
+          <t>Rp10.850.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5772,16 +5772,16 @@
         <v>30</v>
       </c>
       <c r="D70" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp2.675.000</t>
+          <t>Rp2.825.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5803,16 +5803,16 @@
         <v>30</v>
       </c>
       <c r="D71" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rp1.865.000</t>
+          <t>Rp2.635.000</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -5978,16 +5978,16 @@
         <v>324</v>
       </c>
       <c r="D3" t="n">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp16.005.000</t>
+          <t>Rp16.665.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6009,16 +6009,16 @@
         <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp1.075.000</t>
+          <t>Rp1.450.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6040,16 +6040,16 @@
         <v>102</v>
       </c>
       <c r="D5" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp6.200.000</t>
+          <t>Rp7.400.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6071,16 +6071,16 @@
         <v>36</v>
       </c>
       <c r="D6" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp2.010.000</t>
+          <t>Rp2.470.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6133,16 +6133,16 @@
         <v>256</v>
       </c>
       <c r="D8" t="n">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>27.7%</t>
+          <t>28.5%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp31.650.000</t>
+          <t>Rp32.850.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6164,16 +6164,16 @@
         <v>54</v>
       </c>
       <c r="D9" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp1.350.000</t>
+          <t>Rp1.700.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6226,16 +6226,16 @@
         <v>72</v>
       </c>
       <c r="D11" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp2.940.000</t>
+          <t>Rp3.540.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6257,16 +6257,16 @@
         <v>36</v>
       </c>
       <c r="D12" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp1.498.000</t>
+          <t>Rp2.368.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -6350,16 +6350,16 @@
         <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp3.650.000</t>
+          <t>Rp2.550.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6381,16 +6381,16 @@
         <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp4.375.000</t>
+          <t>Rp3.805.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6412,16 +6412,16 @@
         <v>102</v>
       </c>
       <c r="D17" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp4.125.000</t>
+          <t>Rp4.675.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -6649,16 +6649,16 @@
         <v>86</v>
       </c>
       <c r="D3" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp5.250.000</t>
+          <t>Rp6.250.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6711,16 +6711,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp99.000</t>
+          <t>Rp306.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6742,16 +6742,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp11.900.000</t>
+          <t>Rp13.465.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6835,16 +6835,16 @@
         <v>85</v>
       </c>
       <c r="D9" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp9.455.000</t>
+          <t>Rp9.927.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6990,16 +6990,16 @@
         <v>72</v>
       </c>
       <c r="D14" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp3.720.000</t>
+          <t>Rp3.995.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -7052,16 +7052,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp5.650.000</t>
+          <t>Rp6.050.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7114,16 +7114,16 @@
         <v>90</v>
       </c>
       <c r="D18" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp500.000</t>
+          <t>Rp1.500.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7207,16 +7207,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>42.5%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp22.000.000</t>
+          <t>Rp22.600.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp4.197.000</t>
+          <t>Rp4.359.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7331,16 +7331,16 @@
         <v>48</v>
       </c>
       <c r="D25" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp519.000</t>
+          <t>Rp779.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -7362,16 +7362,16 @@
         <v>108</v>
       </c>
       <c r="D26" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp6.130.000</t>
+          <t>Rp6.630.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -7393,16 +7393,16 @@
         <v>36</v>
       </c>
       <c r="D27" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp200.000</t>
+          <t>Rp375.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -7424,16 +7424,16 @@
         <v>96</v>
       </c>
       <c r="D28" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp4.050.000</t>
+          <t>Rp4.300.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -7455,16 +7455,16 @@
         <v>64</v>
       </c>
       <c r="D29" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp3.375.000</t>
+          <t>Rp3.925.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -7486,16 +7486,16 @@
         <v>84</v>
       </c>
       <c r="D30" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp3.740.000</t>
+          <t>Rp3.300.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -7641,16 +7641,16 @@
         <v>187</v>
       </c>
       <c r="D35" t="n">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>36.9%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp13.175.000</t>
+          <t>Rp13.950.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7672,16 +7672,16 @@
         <v>67</v>
       </c>
       <c r="D36" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp3.932.000</t>
+          <t>Rp5.084.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -7703,16 +7703,16 @@
         <v>84</v>
       </c>
       <c r="D37" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp199.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -7827,16 +7827,16 @@
         <v>150</v>
       </c>
       <c r="D41" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>48.7%</t>
+          <t>50.7%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp22.375.000</t>
+          <t>Rp23.425.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -7858,16 +7858,16 @@
         <v>120</v>
       </c>
       <c r="D42" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp2.000.000</t>
+          <t>Rp3.200.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -7889,16 +7889,16 @@
         <v>80</v>
       </c>
       <c r="D43" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp2.300.000</t>
+          <t>Rp2.800.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -7920,16 +7920,16 @@
         <v>64</v>
       </c>
       <c r="D44" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp2.600.000</t>
+          <t>Rp2.800.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -7951,16 +7951,16 @@
         <v>112</v>
       </c>
       <c r="D45" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp9.655.000</t>
+          <t>Rp9.930.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -7982,16 +7982,16 @@
         <v>174</v>
       </c>
       <c r="D46" t="n">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp30.900.000</t>
+          <t>Rp34.500.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -8106,16 +8106,16 @@
         <v>102</v>
       </c>
       <c r="D50" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp13.883.000</t>
+          <t>Rp14.232.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -8199,16 +8199,16 @@
         <v>90</v>
       </c>
       <c r="D53" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp6.600.000</t>
+          <t>Rp6.900.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -8281,21 +8281,21 @@
         <v>72</v>
       </c>
       <c r="D2" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp250.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rp135.000 - Rp185.000</t>
+          <t>Rp125.000 - Rp150.000</t>
         </is>
       </c>
     </row>
@@ -8312,16 +8312,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp5.740.000</t>
+          <t>Rp6.660.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8343,16 +8343,16 @@
         <v>34</v>
       </c>
       <c r="D4" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp1.178.000</t>
+          <t>Rp1.698.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -8374,16 +8374,16 @@
         <v>86</v>
       </c>
       <c r="D5" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>25.6%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp5.800.000</t>
+          <t>Rp6.500.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -8436,16 +8436,16 @@
         <v>48</v>
       </c>
       <c r="D7" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp1.365.000</t>
+          <t>Rp1.915.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -8467,16 +8467,16 @@
         <v>51</v>
       </c>
       <c r="D8" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp520.000</t>
+          <t>Rp1.005.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -8622,16 +8622,16 @@
         <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp4.174.991</t>
+          <t>Rp4.424.991</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -8653,16 +8653,16 @@
         <v>72</v>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp2.300.000</t>
+          <t>Rp3.100.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -8684,16 +8684,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp891.000</t>
+          <t>Rp990.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -8746,16 +8746,16 @@
         <v>54</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp2.560.000</t>
+          <t>Rp2.720.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8808,16 +8808,16 @@
         <v>102</v>
       </c>
       <c r="D19" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>36.3%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp14.350.000</t>
+          <t>Rp15.310.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8901,16 +8901,16 @@
         <v>144</v>
       </c>
       <c r="D22" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp4.035.000</t>
+          <t>Rp3.450.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -8932,16 +8932,16 @@
         <v>36</v>
       </c>
       <c r="D23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp1.835.000</t>
+          <t>Rp1.636.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9087,16 +9087,16 @@
         <v>36</v>
       </c>
       <c r="D28" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp3.000.000</t>
+          <t>Rp2.000.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -9149,16 +9149,16 @@
         <v>54</v>
       </c>
       <c r="D30" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp2.900.000</t>
+          <t>Rp2.675.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -9211,16 +9211,16 @@
         <v>34</v>
       </c>
       <c r="D32" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp2.285.000</t>
+          <t>Rp2.805.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -9304,16 +9304,16 @@
         <v>51</v>
       </c>
       <c r="D35" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp1.770.000</t>
+          <t>Rp1.955.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -9335,16 +9335,16 @@
         <v>72</v>
       </c>
       <c r="D36" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp1.436.000</t>
+          <t>Rp1.733.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -9366,16 +9366,16 @@
         <v>54</v>
       </c>
       <c r="D37" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp3.525.000</t>
+          <t>Rp2.525.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -9459,16 +9459,16 @@
         <v>68</v>
       </c>
       <c r="D40" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp1.592.000</t>
+          <t>Rp796.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -9490,16 +9490,16 @@
         <v>64</v>
       </c>
       <c r="D41" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp1.400.000</t>
+          <t>Rp1.800.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-27.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-27.xlsx
@@ -730,16 +730,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp5.572.987</t>
+          <t>Rp5.128.987</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>162</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>37.7%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp13.714.500</t>
+          <t>Rp14.044.500</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1133,16 +1133,16 @@
         <v>102</v>
       </c>
       <c r="D23" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp4.250.000</t>
+          <t>Rp4.400.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>72</v>
       </c>
       <c r="D25" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp3.600.000</t>
+          <t>Rp4.100.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1350,16 +1350,16 @@
         <v>54</v>
       </c>
       <c r="D30" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp1.840.000</t>
+          <t>Rp2.080.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1474,16 +1474,16 @@
         <v>68</v>
       </c>
       <c r="D34" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp3.595.000</t>
+          <t>Rp3.915.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1784,16 +1784,16 @@
         <v>72</v>
       </c>
       <c r="D44" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp8.324.000</t>
+          <t>Rp9.624.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -1815,16 +1815,16 @@
         <v>198</v>
       </c>
       <c r="D45" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp1.950.000</t>
+          <t>Rp1.800.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2373,16 +2373,16 @@
         <v>72</v>
       </c>
       <c r="D63" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp3.045.000</t>
+          <t>Rp3.135.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2683,16 +2683,16 @@
         <v>72</v>
       </c>
       <c r="D73" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp925.000</t>
+          <t>Rp1.000.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2869,16 +2869,16 @@
         <v>108</v>
       </c>
       <c r="D79" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rp2.850.000</t>
+          <t>Rp3.075.000</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -2900,16 +2900,16 @@
         <v>114</v>
       </c>
       <c r="D80" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rp2.975.000</t>
+          <t>Rp3.150.000</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -2931,16 +2931,16 @@
         <v>126</v>
       </c>
       <c r="D81" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>30.2%</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rp5.163.000</t>
+          <t>Rp5.262.000</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3788,16 +3788,16 @@
         <v>68</v>
       </c>
       <c r="D6" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp690.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -4160,16 +4160,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp6.350.000</t>
+          <t>Rp7.150.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4470,16 +4470,16 @@
         <v>170</v>
       </c>
       <c r="D28" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp16.200.000</t>
+          <t>Rp16.475.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4811,16 +4811,16 @@
         <v>32</v>
       </c>
       <c r="D39" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp6.800.000</t>
+          <t>Rp6.200.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5555,16 +5555,16 @@
         <v>64</v>
       </c>
       <c r="D63" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp8.950.000</t>
+          <t>Rp9.450.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -5617,16 +5617,16 @@
         <v>90</v>
       </c>
       <c r="D65" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rp9.400.000</t>
+          <t>Rp9.650.000</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -5947,16 +5947,16 @@
         <v>18</v>
       </c>
       <c r="D2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp320.000</t>
+          <t>Rp480.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6040,16 +6040,16 @@
         <v>102</v>
       </c>
       <c r="D5" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp7.400.000</t>
+          <t>Rp7.900.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6649,16 +6649,16 @@
         <v>86</v>
       </c>
       <c r="D3" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp6.250.000</t>
+          <t>Rp7.950.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6711,16 +6711,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp306.000</t>
+          <t>Rp543.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6897,16 +6897,16 @@
         <v>216</v>
       </c>
       <c r="D11" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp17.161.500</t>
+          <t>Rp17.398.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -7362,16 +7362,16 @@
         <v>108</v>
       </c>
       <c r="D26" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp6.630.000</t>
+          <t>Rp6.460.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -7641,16 +7641,16 @@
         <v>187</v>
       </c>
       <c r="D35" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp13.950.000</t>
+          <t>Rp14.000.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7672,16 +7672,16 @@
         <v>67</v>
       </c>
       <c r="D36" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp5.084.000</t>
+          <t>Rp5.272.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -7734,16 +7734,16 @@
         <v>170</v>
       </c>
       <c r="D38" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp4.900.000</t>
+          <t>Rp4.975.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -8653,16 +8653,16 @@
         <v>72</v>
       </c>
       <c r="D14" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp3.100.000</t>
+          <t>Rp3.200.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -8901,16 +8901,16 @@
         <v>144</v>
       </c>
       <c r="D22" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp3.450.000</t>
+          <t>Rp3.810.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -8963,16 +8963,16 @@
         <v>54</v>
       </c>
       <c r="D24" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp4.574.994</t>
+          <t>Rp4.824.994</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
